--- a/History/Summary.xlsx
+++ b/History/Summary.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
     </row>
@@ -450,7 +450,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:31:55</t>
+          <t>11:08:25</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5000</v>
+        <v>4333</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Location: [Connect Geolocation API here]</t>
+          <t>Vijayawada, Andhra Pradesh, IN</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2650</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="4">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2650</v>
+        <v>3211</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/History/Summary.xlsx
+++ b/History/Summary.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -450,7 +450,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:08:25</t>
+          <t>11:24:58</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sunny</t>
+          <t>swiggy</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4333</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vijayawada, Andhra Pradesh, IN</t>
+          <t>Hyderabad, Telangana, IN</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3211</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="4">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,14 +588,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sunny</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3211</v>
+        <v>5000</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>swiggy</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
